--- a/data/manual/mensajes.xlsx
+++ b/data/manual/mensajes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_edobru\Desktop\Bancomext\Indicadores\data\manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ADBB48-5A09-4713-A63D-D0CB33DF4A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51800BF-DE89-4772-B41F-4FBBC7EB106D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{8DCF18AD-E6F7-4D60-9DD0-0BD25E1283AA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8DCF18AD-E6F7-4D60-9DD0-0BD25E1283AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="110">
   <si>
     <t>variable</t>
   </si>
@@ -255,9 +255,6 @@
     <t>En junio de 2025 fue de 2.60 por ciento.</t>
   </si>
   <si>
-    <t>En el primer trimestre de 2026 aumentó 1.93% anual con respecto al mismo periodo de 2025.</t>
-  </si>
-  <si>
     <t>El sector primario registró un incremento anual de 4.8%.</t>
   </si>
   <si>
@@ -267,9 +264,6 @@
     <t>Las actividades terciarias registraron un incremento anual de 2.3%.</t>
   </si>
   <si>
-    <t>En el primer trimestre de 2026 disminuyó 0.34% con respecto al cuarto trimestre de 2025.</t>
-  </si>
-  <si>
     <t>En el segundo trimestre de 2026 el sector primario registró un alza mensual de 2.4%.</t>
   </si>
   <si>
@@ -291,9 +285,6 @@
     <t>La disminución en junio de 2026 se explicó por caídas del sector primario (-3.6%) y terciario (-0.6%). Por su parte, el secundario registró un aumento (0.2%).</t>
   </si>
   <si>
-    <t>Con relación a estas últimas, disminuyeron las de uso intermedio no petrolero (-4.0%) y las de bienes de capital (-0.4%).</t>
-  </si>
-  <si>
     <t>Inflación subyacente: 3.93% anual (vs. 3.95% en julio).</t>
   </si>
   <si>
@@ -309,7 +300,76 @@
     <t>Inflación no subyacente: 0.18% (vs. -0.67% julio).</t>
   </si>
   <si>
-    <t>vs. 18.00 cierre 2025. Apreciación de 5.76% en lo que va de 2026.</t>
+    <t>En el segundo trimestre de 2026 aumentó 1.93% anual con respecto al mismo periodo de 2025.</t>
+  </si>
+  <si>
+    <t>En el segundo trimestre de 2026 aumentó 1.34% con respecto al primer trimestre de 2026.</t>
+  </si>
+  <si>
+    <t>Se registró un aumento en bienes importados de 1.7% y en bienes y servicios de consumo nacional de 0.8%.</t>
+  </si>
+  <si>
+    <t>Rompe con una racha de tres meses de variaciones mensuales positivas.</t>
+  </si>
+  <si>
+    <t>Registró una disminución de 0.4% en el consumo nacional, mientras que en bienes importados se registró una caída de 1.4%.</t>
+  </si>
+  <si>
+    <t>Acumula tres aumentos anuales después de diecinueve caídas anuales consecutivas.</t>
+  </si>
+  <si>
+    <t>La inversión pública creció anual 18.1% en junio de 2026, mientras que la privada aumentó 6.0%.</t>
+  </si>
+  <si>
+    <t>La inversión pública aumentó mensual 10.9%, pero la inversión privada disminuyó 0.7%.</t>
+  </si>
+  <si>
+    <t>Cifra récord de 34,968 millones de dólares para un primer semestre.</t>
+  </si>
+  <si>
+    <t>Las nuevas inversiones cayeron (-)13.4%, mientras que la reinversión de utilidades aumentó un 7.1%. Por su parte, las cuentas entre compañías registraron una disminución de (-)41.6%.</t>
+  </si>
+  <si>
+    <t>El valor de las exportaciones en enero-julio de 2026 es 27% mayor al del mismo periodo de 2025.</t>
+  </si>
+  <si>
+    <t>En julio, las petroleras aumentaron anual 6.4% y las no petroleras 44.4%. En estas últimas destacaron las extractivas (89.5%) y manufacturas no automotrices (64.6%). Agropecuarias cayeron (6.1%).</t>
+  </si>
+  <si>
+    <t>Las automotrices disminuyeron 3.3% (habían crecido 6.0% en mayo) y las manufactureras no automotrices crecieron 14.3% (acumulan ocho aumentos mensuales consecutivos).</t>
+  </si>
+  <si>
+    <t>Las petroleras descendieron 8.4% y las agropecuarias crecieron 5.5%.</t>
+  </si>
+  <si>
+    <t>El valor de las importaciones en enero-julio de 2026 es 25.1% mayor al del mismo periodo de 2025.</t>
+  </si>
+  <si>
+    <t>En julio, las petroleras aumentaron 39.9% y las no petroleras crecieron 44.0%. En las últimas destacaron las alzas de bienes de consumo (9.3%), de bienes de uso intermedio (54.8%) y las de bienes de capital (9.1%).</t>
+  </si>
+  <si>
+    <t>Crecieron tanto las petroleras (2.0%) como las no petroleras (16.2%). Con relación a estas últimas, incrementaron las de uso intermedio no petrolero (19.8%) y las de bienes de capital (7.3%)</t>
+  </si>
+  <si>
+    <t>En pesos constantes cayeron 12.52% debido en gran medida a la apreciación del tipo de cambio.</t>
+  </si>
+  <si>
+    <t>En pesos constantes incrementaron 0.94% tras una depreciación del tipo de cambio en julio.</t>
+  </si>
+  <si>
+    <t>vs. 18.00 cierre 2025. Apreciación de 5.81% en lo que va de 2026.</t>
+  </si>
+  <si>
+    <t>Tipo de cambio promedio del 2026: 17.41 vs. 18.4 de Pre-Criterios 2027.</t>
+  </si>
+  <si>
+    <t>vs. 2.80% en junio.</t>
+  </si>
+  <si>
+    <t>Refleja una disminución respecto a la cifra de junio.</t>
+  </si>
+  <si>
+    <t>En junio de 2025 fue de 2.58 por ciento.</t>
   </si>
 </sst>
 </file>
@@ -681,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711DAF1C-F729-4A08-B32A-80DE6CBF4CE4}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -708,7 +768,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -719,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -730,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -741,7 +801,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -752,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -763,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -774,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -785,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -796,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -807,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -818,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -829,7 +889,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -862,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -873,7 +933,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -884,7 +944,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -895,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -906,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -917,7 +977,7 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -928,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -939,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -950,7 +1010,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -961,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -972,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -983,7 +1043,7 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -994,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1005,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -1016,18 +1076,18 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1035,21 +1095,21 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1060,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1071,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1082,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1090,10 +1150,10 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1101,10 +1161,10 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1112,21 +1172,21 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1137,29 +1197,29 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1170,7 +1230,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1178,21 +1238,21 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1203,7 +1263,7 @@
         <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1214,18 +1274,7 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
